--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-09-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_24-09-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{024A2A72-1437-4092-8E2D-D0FF6CDA68B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D269BD-A8C6-4B0C-8326-5FED2E023C28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11070" yWindow="1590" windowWidth="14880" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9075" yWindow="2085" windowWidth="14880" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="268">
   <si>
     <t>SKU</t>
   </si>
@@ -571,48 +571,12 @@
     <t>£23.13</t>
   </si>
   <si>
-    <t>£19.27</t>
-  </si>
-  <si>
-    <t>£24.26</t>
-  </si>
-  <si>
-    <t>£27.59</t>
-  </si>
-  <si>
-    <t>£31.06</t>
-  </si>
-  <si>
-    <t>£40.83</t>
-  </si>
-  <si>
-    <t>£43.06</t>
-  </si>
-  <si>
-    <t>£55.70</t>
-  </si>
-  <si>
-    <t>£74.88</t>
-  </si>
-  <si>
-    <t>£66.58</t>
-  </si>
-  <si>
-    <t>£78.08</t>
-  </si>
-  <si>
     <t>£126.96</t>
   </si>
   <si>
     <t>£122.43</t>
   </si>
   <si>
-    <t>£463.00</t>
-  </si>
-  <si>
-    <t>£370.40</t>
-  </si>
-  <si>
     <t>£14.39</t>
   </si>
   <si>
@@ -821,6 +785,45 @@
   </si>
   <si>
     <t>£716.05</t>
+  </si>
+  <si>
+    <t>£25.00</t>
+  </si>
+  <si>
+    <t>£29.11</t>
+  </si>
+  <si>
+    <t>£33.11</t>
+  </si>
+  <si>
+    <t>£37.27</t>
+  </si>
+  <si>
+    <t>£48.99</t>
+  </si>
+  <si>
+    <t>£51.67</t>
+  </si>
+  <si>
+    <t>£66.84</t>
+  </si>
+  <si>
+    <t>£79.89</t>
+  </si>
+  <si>
+    <t>£89.86</t>
+  </si>
+  <si>
+    <t>£93.69</t>
+  </si>
+  <si>
+    <t>£99.37</t>
+  </si>
+  <si>
+    <t>£657.00</t>
+  </si>
+  <si>
+    <t>£711.4</t>
   </si>
 </sst>
 </file>
@@ -1264,7 +1267,7 @@
         <v>66</v>
       </c>
       <c r="F2" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="G2" t="s">
         <v>88</v>
@@ -1291,16 +1294,16 @@
         <v>182</v>
       </c>
       <c r="O2" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
       <c r="P2" t="s">
         <v>181</v>
       </c>
       <c r="Q2" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="R2" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:18" x14ac:dyDescent="0.25">
@@ -1320,7 +1323,7 @@
         <v>67</v>
       </c>
       <c r="F3" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="G3" t="s">
         <v>89</v>
@@ -1344,19 +1347,19 @@
         <v>167</v>
       </c>
       <c r="N3" t="s">
-        <v>183</v>
+        <v>255</v>
       </c>
       <c r="O3" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
       <c r="P3" t="s">
         <v>181</v>
       </c>
       <c r="Q3" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="R3" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
     </row>
     <row r="4" spans="1:18" x14ac:dyDescent="0.25">
@@ -1376,7 +1379,7 @@
         <v>87</v>
       </c>
       <c r="F4" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
       <c r="G4" t="s">
         <v>90</v>
@@ -1400,19 +1403,19 @@
         <v>168</v>
       </c>
       <c r="N4" t="s">
-        <v>90</v>
+        <v>256</v>
       </c>
       <c r="O4" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
       <c r="P4" t="s">
         <v>181</v>
       </c>
       <c r="Q4" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="R4" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.25">
@@ -1456,7 +1459,7 @@
         <v>169</v>
       </c>
       <c r="N5" t="s">
-        <v>184</v>
+        <v>257</v>
       </c>
       <c r="O5" t="s">
         <v>69</v>
@@ -1465,10 +1468,10 @@
         <v>181</v>
       </c>
       <c r="Q5" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="R5" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
@@ -1488,7 +1491,7 @@
         <v>70</v>
       </c>
       <c r="F6" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
       <c r="G6" t="s">
         <v>92</v>
@@ -1512,19 +1515,19 @@
         <v>170</v>
       </c>
       <c r="N6" t="s">
-        <v>185</v>
+        <v>258</v>
       </c>
       <c r="O6" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="P6" t="s">
         <v>181</v>
       </c>
       <c r="Q6" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
       <c r="R6" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
@@ -1544,7 +1547,7 @@
         <v>71</v>
       </c>
       <c r="F7" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="G7" t="s">
         <v>93</v>
@@ -1568,19 +1571,19 @@
         <v>171</v>
       </c>
       <c r="N7" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="O7" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
       <c r="P7" t="s">
         <v>181</v>
       </c>
       <c r="Q7" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
       <c r="R7" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
@@ -1600,7 +1603,7 @@
         <v>72</v>
       </c>
       <c r="F8" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="G8" t="s">
         <v>94</v>
@@ -1612,7 +1615,7 @@
         <v>131</v>
       </c>
       <c r="J8" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
       <c r="K8" t="s">
         <v>158</v>
@@ -1624,7 +1627,7 @@
         <v>172</v>
       </c>
       <c r="N8" t="s">
-        <v>186</v>
+        <v>259</v>
       </c>
       <c r="O8" t="s">
         <v>71</v>
@@ -1633,10 +1636,10 @@
         <v>181</v>
       </c>
       <c r="Q8" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="R8" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
@@ -1656,7 +1659,7 @@
         <v>73</v>
       </c>
       <c r="F9" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
       <c r="G9" t="s">
         <v>95</v>
@@ -1680,19 +1683,19 @@
         <v>173</v>
       </c>
       <c r="N9" t="s">
-        <v>187</v>
+        <v>260</v>
       </c>
       <c r="O9" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="P9" t="s">
         <v>181</v>
       </c>
       <c r="Q9" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="R9" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
@@ -1724,7 +1727,7 @@
         <v>133</v>
       </c>
       <c r="J10" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c r="K10" t="s">
         <v>159</v>
@@ -1736,19 +1739,19 @@
         <v>87</v>
       </c>
       <c r="N10" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="O10" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="P10" t="s">
         <v>181</v>
       </c>
       <c r="Q10" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
       <c r="R10" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
@@ -1768,7 +1771,7 @@
         <v>74</v>
       </c>
       <c r="F11" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
       <c r="G11" t="s">
         <v>97</v>
@@ -1792,19 +1795,19 @@
         <v>174</v>
       </c>
       <c r="N11" t="s">
-        <v>188</v>
+        <v>261</v>
       </c>
       <c r="O11" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="P11" t="s">
         <v>181</v>
       </c>
       <c r="Q11" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="R11" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
@@ -1824,7 +1827,7 @@
         <v>87</v>
       </c>
       <c r="F12" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
       <c r="G12" t="s">
         <v>98</v>
@@ -1848,7 +1851,7 @@
         <v>175</v>
       </c>
       <c r="N12" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="O12" t="s">
         <v>75</v>
@@ -1857,7 +1860,7 @@
         <v>181</v>
       </c>
       <c r="Q12" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="R12" t="s">
         <v>87</v>
@@ -1880,7 +1883,7 @@
         <v>76</v>
       </c>
       <c r="F13" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
       <c r="G13" t="s">
         <v>99</v>
@@ -1892,7 +1895,7 @@
         <v>136</v>
       </c>
       <c r="J13" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="K13" t="s">
         <v>161</v>
@@ -1904,19 +1907,19 @@
         <v>176</v>
       </c>
       <c r="N13" t="s">
-        <v>189</v>
+        <v>262</v>
       </c>
       <c r="O13" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="P13" t="s">
         <v>181</v>
       </c>
       <c r="Q13" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="R13" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
@@ -1936,7 +1939,7 @@
         <v>87</v>
       </c>
       <c r="F14" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
       <c r="G14" t="s">
         <v>100</v>
@@ -1948,7 +1951,7 @@
         <v>137</v>
       </c>
       <c r="J14" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="K14" t="s">
         <v>162</v>
@@ -1960,16 +1963,16 @@
         <v>177</v>
       </c>
       <c r="N14" t="s">
-        <v>190</v>
+        <v>263</v>
       </c>
       <c r="O14" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
       <c r="P14" t="s">
         <v>181</v>
       </c>
       <c r="Q14" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="R14" t="s">
         <v>87</v>
@@ -1992,7 +1995,7 @@
         <v>87</v>
       </c>
       <c r="F15" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
       <c r="G15" t="s">
         <v>101</v>
@@ -2004,7 +2007,7 @@
         <v>138</v>
       </c>
       <c r="J15" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="K15" t="s">
         <v>163</v>
@@ -2016,16 +2019,16 @@
         <v>178</v>
       </c>
       <c r="N15" t="s">
-        <v>191</v>
+        <v>264</v>
       </c>
       <c r="O15" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="P15" t="s">
         <v>181</v>
       </c>
       <c r="Q15" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
       <c r="R15" t="s">
         <v>87</v>
@@ -2048,7 +2051,7 @@
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
       <c r="G16" t="s">
         <v>102</v>
@@ -2072,19 +2075,19 @@
         <v>179</v>
       </c>
       <c r="N16" t="s">
-        <v>192</v>
+        <v>265</v>
       </c>
       <c r="O16" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
       <c r="P16" t="s">
         <v>181</v>
       </c>
       <c r="Q16" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="R16" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="17" spans="1:18" x14ac:dyDescent="0.25">
@@ -2095,10 +2098,10 @@
         <v>57</v>
       </c>
       <c r="C17" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="D17" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
       <c r="E17" t="s">
         <v>87</v>
@@ -2172,7 +2175,7 @@
         <v>87</v>
       </c>
       <c r="J18" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
       <c r="K18" t="s">
         <v>87</v>
@@ -2184,10 +2187,10 @@
         <v>87</v>
       </c>
       <c r="N18" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="O18" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
       <c r="P18" t="s">
         <v>181</v>
@@ -2240,10 +2243,10 @@
         <v>87</v>
       </c>
       <c r="N19" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="O19" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="P19" t="s">
         <v>181</v>
@@ -2252,7 +2255,7 @@
         <v>87</v>
       </c>
       <c r="R19" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
@@ -2396,7 +2399,7 @@
         <v>87</v>
       </c>
       <c r="J22" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
       <c r="K22" t="s">
         <v>87</v>
@@ -2455,7 +2458,7 @@
         <v>87</v>
       </c>
       <c r="K23" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
       <c r="L23" t="s">
         <v>87</v>
@@ -2464,10 +2467,10 @@
         <v>180</v>
       </c>
       <c r="N23" t="s">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="O23" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="P23" t="s">
         <v>87</v>
@@ -2476,7 +2479,7 @@
         <v>87</v>
       </c>
       <c r="R23" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
@@ -2511,7 +2514,7 @@
         <v>87</v>
       </c>
       <c r="K24" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="L24" t="s">
         <v>87</v>
@@ -2520,10 +2523,10 @@
         <v>181</v>
       </c>
       <c r="N24" t="s">
-        <v>195</v>
+        <v>266</v>
       </c>
       <c r="O24" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="P24" t="s">
         <v>87</v>
@@ -2532,7 +2535,7 @@
         <v>87</v>
       </c>
       <c r="R24" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
@@ -2576,10 +2579,10 @@
         <v>181</v>
       </c>
       <c r="N25" t="s">
-        <v>196</v>
+        <v>267</v>
       </c>
       <c r="O25" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
       <c r="P25" t="s">
         <v>87</v>
@@ -2588,7 +2591,7 @@
         <v>87</v>
       </c>
       <c r="R25" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
     </row>
   </sheetData>
